--- a/avito-feed-legkovye/fleet-legkovye.xlsx
+++ b/avito-feed-legkovye/fleet-legkovye.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="BR5" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGAUDIA5LSPORTBA</t>
+          <t>ZZPEF486F137A3119</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="BR6" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGBMWX630D</t>
+          <t>ZZP201B7187EC2882</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="BR7" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGGACM8</t>
+          <t>ZZPC666666E51FB05</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="BR8" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGGACTRUMPCHIM8G</t>
+          <t>ZZP89D754E6200EAE</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="BR9" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGLEXUSGX550</t>
+          <t>ZZP0815BA9392895C</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="BR10" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGLEXUSRX500H</t>
+          <t>ZZP2786D3584A8F87</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="BR11" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGMAZDACX30</t>
+          <t>ZZP6020E59663FD86</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="BR12" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGTOYOTALANDCRUI</t>
+          <t>ZZP1DC5202AEEC2C4</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="BR13" s="8" t="inlineStr">
         <is>
-          <t>ZZPENDINGVOLVOXC90</t>
+          <t>ZZP34515598A894C2</t>
         </is>
       </c>
     </row>
